--- a/data/trans_dic/P44A$endoscopia-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P44A$endoscopia-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado al menos una endoscopia para detectar cáncer de colon</t>
+          <t>Población a la que le han realizado al menos una endoscopia para detectar cáncer de colon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>46,35; 76,37</t>
+          <t>47,2; 76,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44,93; 71,19</t>
+          <t>45,87; 72,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36,68; 50,14</t>
+          <t>36,95; 51,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54,51; 78,56</t>
+          <t>52,94; 76,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>42,14; 69,0</t>
+          <t>41,1; 67,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,11; 47,21</t>
+          <t>36,73; 47,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,3; 74,17</t>
+          <t>55,37; 73,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>47,35; 66,85</t>
+          <t>46,99; 65,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>38,23; 46,49</t>
+          <t>38,74; 47,43</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>43,83; 73,73</t>
+          <t>43,56; 74,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40,51; 63,33</t>
+          <t>39,61; 62,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37,29; 90,71</t>
+          <t>36,93; 90,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34,75; 72,26</t>
+          <t>34,25; 73,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,89; 73,02</t>
+          <t>37,48; 71,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,6; 38,97</t>
+          <t>29,71; 38,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,7; 68,14</t>
+          <t>46,05; 68,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>43,13; 62,27</t>
+          <t>43,54; 62,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35,15; 82,4</t>
+          <t>35,31; 82,67</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31,58; 87,28</t>
+          <t>31,09; 87,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,13; 61,24</t>
+          <t>23,39; 63,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41,41; 57,11</t>
+          <t>41,64; 57,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,92; 80,62</t>
+          <t>22,96; 81,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,53; 80,46</t>
+          <t>25,74; 80,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,87; 39,72</t>
+          <t>25,24; 40,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,42; 77,78</t>
+          <t>35,37; 77,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>31,44; 63,75</t>
+          <t>30,12; 63,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36,58; 48,33</t>
+          <t>36,64; 48,07</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>51,6; 71,36</t>
+          <t>52,35; 71,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43,54; 59,81</t>
+          <t>43,82; 60,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41,48; 83,12</t>
+          <t>41,39; 83,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51,84; 72,26</t>
+          <t>51,56; 70,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45,52; 65,45</t>
+          <t>45,08; 64,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,06; 39,47</t>
+          <t>33,29; 39,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,13; 68,78</t>
+          <t>53,98; 67,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>47,41; 59,61</t>
+          <t>47,03; 59,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,73; 73,03</t>
+          <t>38,84; 74,47</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado al menos una endoscopia para detectar cáncer de colon</t>
+          <t>Población a la que le han realizado al menos una endoscopia para detectar cáncer de colon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20884; 34410</t>
+          <t>21267; 34683</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23236; 36818</t>
+          <t>23722; 37308</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51522; 70427</t>
+          <t>51904; 71864</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34295; 49422</t>
+          <t>33304; 48307</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26177; 42861</t>
+          <t>25526; 41849</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>61354; 80219</t>
+          <t>62406; 80651</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>59711; 80076</t>
+          <t>59781; 79589</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>53899; 76094</t>
+          <t>53489; 74026</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>118644; 144300</t>
+          <t>120248; 147208</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21803; 36680</t>
+          <t>21669; 36841</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31632; 49445</t>
+          <t>30927; 48902</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>190390; 463179</t>
+          <t>188560; 461292</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10580; 21996</t>
+          <t>10427; 22490</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13081; 26612</t>
+          <t>13659; 25980</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66011; 86904</t>
+          <t>66265; 86645</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35844; 54639</t>
+          <t>36925; 55203</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>49389; 71310</t>
+          <t>49866; 71171</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>257878; 604516</t>
+          <t>259063; 606503</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4599; 12711</t>
+          <t>4528; 12722</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6695; 17725</t>
+          <t>6770; 18398</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51237; 70671</t>
+          <t>51526; 71490</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2862; 10069</t>
+          <t>2867; 10119</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4122; 12988</t>
+          <t>4155; 12990</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22037; 33831</t>
+          <t>21493; 34228</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10124; 21042</t>
+          <t>9569; 20955</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14174; 28744</t>
+          <t>13579; 28646</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>76420; 100977</t>
+          <t>76539; 100429</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>56432; 78039</t>
+          <t>57249; 77847</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69110; 94943</t>
+          <t>69564; 96353</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>321402; 644058</t>
+          <t>320734; 644745</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>54870; 76486</t>
+          <t>54574; 74671</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>52211; 75076</t>
+          <t>51702; 74095</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>158068; 188697</t>
+          <t>159143; 189444</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>116498; 148014</t>
+          <t>116173; 146191</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>129631; 162995</t>
+          <t>128610; 162161</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>485247; 914955</t>
+          <t>486587; 933104</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P44A$endoscopia-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P44A$endoscopia-Estudios-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,64%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>47,2; 76,98</t>
+          <t>45,6; 75,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>45,87; 72,14</t>
+          <t>45,21; 70,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36,95; 51,16</t>
+          <t>36,75; 51,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52,94; 76,78</t>
+          <t>54,75; 78,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>41,1; 67,37</t>
+          <t>42,95; 69,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,73; 47,46</t>
+          <t>36,28; 46,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,37; 73,72</t>
+          <t>54,59; 74,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>46,99; 65,03</t>
+          <t>47,74; 66,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>38,74; 47,43</t>
+          <t>38,7; 46,86</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>37,4%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>43,56; 74,06</t>
+          <t>44,37; 73,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39,61; 62,63</t>
+          <t>39,74; 62,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36,93; 90,34</t>
+          <t>34,5; 44,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34,25; 73,88</t>
+          <t>30,78; 71,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,48; 71,29</t>
+          <t>38,12; 70,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,71; 38,85</t>
+          <t>30,12; 39,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,05; 68,84</t>
+          <t>45,2; 68,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>43,54; 62,15</t>
+          <t>42,7; 62,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35,31; 82,67</t>
+          <t>33,96; 41,13</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,02%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31,09; 87,36</t>
+          <t>36,35; 87,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,39; 63,57</t>
+          <t>24,87; 62,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41,64; 57,77</t>
+          <t>41,88; 58,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,96; 81,02</t>
+          <t>22,55; 79,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,74; 80,47</t>
+          <t>26,39; 81,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,24; 40,19</t>
+          <t>24,68; 38,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,37; 77,46</t>
+          <t>35,01; 77,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,12; 63,54</t>
+          <t>31,41; 62,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36,64; 48,07</t>
+          <t>37,01; 47,67</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>39,96%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>52,35; 71,18</t>
+          <t>50,73; 71,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43,82; 60,7</t>
+          <t>44,45; 59,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41,39; 83,21</t>
+          <t>39,49; 46,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51,56; 70,55</t>
+          <t>50,69; 70,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45,08; 64,6</t>
+          <t>45,31; 64,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,29; 39,62</t>
+          <t>33,4; 39,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,98; 67,93</t>
+          <t>53,47; 67,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>47,03; 59,3</t>
+          <t>46,84; 59,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,84; 74,47</t>
+          <t>37,41; 42,39</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61706</t>
+          <t>66204</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70681</t>
+          <t>77206</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>132387</t>
+          <t>143410</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21267; 34683</t>
+          <t>20547; 34084</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23722; 37308</t>
+          <t>23379; 36357</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51904; 71864</t>
+          <t>54941; 77295</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33304; 48307</t>
+          <t>34445; 49547</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>25526; 41849</t>
+          <t>26676; 43152</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>62406; 80651</t>
+          <t>67795; 87525</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>59781; 79589</t>
+          <t>58939; 80166</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>53489; 74026</t>
+          <t>54344; 76022</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>120248; 147208</t>
+          <t>130154; 157602</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>346926</t>
+          <t>115134</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76003</t>
+          <t>84825</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>422928</t>
+          <t>199959</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21669; 36841</t>
+          <t>22074; 36666</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30927; 48902</t>
+          <t>31025; 48656</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>188560; 461292</t>
+          <t>99982; 130146</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10427; 22490</t>
+          <t>9369; 21886</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13659; 25980</t>
+          <t>13892; 25827</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66265; 86645</t>
+          <t>73744; 96250</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36925; 55203</t>
+          <t>36246; 54932</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>49866; 71171</t>
+          <t>48897; 71280</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>259063; 606503</t>
+          <t>181551; 219867</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60588</t>
+          <t>64869</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27620</t>
+          <t>30154</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>88208</t>
+          <t>95023</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4528; 12722</t>
+          <t>5293; 12673</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6770; 18398</t>
+          <t>7199; 17996</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51526; 71490</t>
+          <t>54247; 75141</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2867; 10119</t>
+          <t>2816; 9956</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4155; 12990</t>
+          <t>4260; 13114</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21493; 34228</t>
+          <t>23845; 37032</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9569; 20955</t>
+          <t>9472; 20870</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13579; 28646</t>
+          <t>14163; 28356</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>76539; 100429</t>
+          <t>83687; 107798</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>469220</t>
+          <t>246207</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>174304</t>
+          <t>192185</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>643524</t>
+          <t>438392</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>57249; 77847</t>
+          <t>55486; 78290</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69564; 96353</t>
+          <t>70560; 94667</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>320734; 644745</t>
+          <t>224605; 266587</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>54574; 74671</t>
+          <t>53655; 75099</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>51702; 74095</t>
+          <t>51968; 74129</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>159143; 189444</t>
+          <t>176466; 209550</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>116173; 146191</t>
+          <t>115078; 145219</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>128610; 162161</t>
+          <t>128072; 162920</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>486587; 933104</t>
+          <t>410363; 465037</t>
         </is>
       </c>
     </row>
